--- a/sim/audit/data_audit_recompute.xlsx
+++ b/sim/audit/data_audit_recompute.xlsx
@@ -3391,10 +3391,10 @@
         <v>1.85</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.828731</v>
+        <v>0.845467</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.101329</v>
+        <v>0.084593</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -3418,10 +3418,10 @@
         <v>0.718946</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.574761</v>
+        <v>0.586368</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.595813</v>
+        <v>0.607845</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>1.9</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.829345</v>
+        <v>0.851217</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.100145</v>
+        <v>0.078273</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0.706744</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.58523</v>
+        <v>0.600665</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.586135</v>
+        <v>0.601593</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>0</v>
@@ -3543,10 +3543,10 @@
         <v>1.95</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.8304820000000001</v>
+        <v>0.8527979999999999</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.098389</v>
+        <v>0.076073</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -3570,10 +3570,10 @@
         <v>0.701417</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.5925010000000001</v>
+        <v>0.608421</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.582515</v>
+        <v>0.598167</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0</v>
@@ -3619,10 +3619,10 @@
         <v>2</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.831483</v>
+        <v>0.852951</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.09679400000000001</v>
+        <v>0.075326</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
@@ -3646,10 +3646,10 @@
         <v>0.696864</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.593186</v>
+        <v>0.608502</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.579431</v>
+        <v>0.594391</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>1.85</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.9388300000000001</v>
+        <v>0.959183</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.047856</v>
+        <v>0.027503</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
@@ -4228,10 +4228,10 @@
         <v>0.926107</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.851382</v>
+        <v>0.869839</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.869456</v>
+        <v>0.888306</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
@@ -4247,10 +4247,10 @@
         <v>1.9</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.939436</v>
+        <v>0.9598640000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.047614</v>
+        <v>0.027186</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0.923517</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.8629019999999999</v>
+        <v>0.8816659999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.867586</v>
+        <v>0.886451</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>0</v>
@@ -4293,10 +4293,10 @@
         <v>1.95</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.9409459999999999</v>
+        <v>0.960224</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.046277</v>
+        <v>0.026999</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0.9210429999999999</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.868542</v>
+        <v>0.886337</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.8666509999999999</v>
+        <v>0.8844070000000001</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>0</v>
@@ -4339,10 +4339,10 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.942373</v>
+        <v>0.960427</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.044946</v>
+        <v>0.026892</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>0</v>
@@ -4366,10 +4366,10 @@
         <v>0.9185990000000001</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.870327</v>
+        <v>0.887</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.865663</v>
+        <v>0.882247</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0</v>
@@ -7458,10 +7458,10 @@
         <v>0.667</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.952339</v>
+        <v>0.9630649999999999</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.033503</v>
+        <v>0.022777</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>6.2e-05</v>
@@ -7485,10 +7485,10 @@
         <v>0.932316</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.868597</v>
+        <v>0.87838</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.887881</v>
+        <v>0.897881</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
@@ -7505,10 +7505,10 @@
         <v>0.8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.962929</v>
+        <v>0.970672</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.022878</v>
+        <v>0.015135</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>7.2e-05</v>
@@ -7532,10 +7532,10 @@
         <v>0.932316</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.874636</v>
+        <v>0.881669</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>0.8977540000000001</v>
+        <v>0.904973</v>
       </c>
       <c r="O3" s="3" t="n">
         <v>0</v>
@@ -7552,10 +7552,10 @@
         <v>0.9</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.970457</v>
+        <v>0.976079</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.015325</v>
+        <v>0.009703</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>8.000000000000001e-05</v>
@@ -7579,10 +7579,10 @@
         <v>0.932316</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.878915</v>
+        <v>0.884007</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.904772</v>
+        <v>0.910014</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
@@ -7599,10 +7599,10 @@
         <v>0.667</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.954833</v>
+        <v>0.965619</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.033498</v>
+        <v>0.022712</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>4.4e-05</v>
@@ -7626,10 +7626,10 @@
         <v>0.943885</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.887143</v>
+        <v>0.897165</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.901253</v>
+        <v>0.911433</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>0</v>
@@ -7646,10 +7646,10 @@
         <v>0.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.965516</v>
+        <v>0.973302</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.022869</v>
+        <v>0.015083</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>5.2e-05</v>
@@ -7673,10 +7673,10 @@
         <v>0.943885</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.894302</v>
+        <v>0.901514</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.911336</v>
+        <v>0.918685</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
@@ -7693,10 +7693,10 @@
         <v>0.9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.9731109999999999</v>
+        <v>0.978764</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.015314</v>
+        <v>0.00966</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>5.7e-05</v>
@@ -7720,10 +7720,10 @@
         <v>0.943885</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.899381</v>
+        <v>0.904606</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.918504</v>
+        <v>0.923841</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0</v>
@@ -7740,10 +7740,10 @@
         <v>0.667</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.962986</v>
+        <v>0.980537</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.020925</v>
+        <v>0.003373</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>8.8e-05</v>
@@ -7767,10 +7767,10 @@
         <v>0.933376</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.873845</v>
+        <v>0.889772</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.898829</v>
+        <v>0.91521</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
@@ -7787,10 +7787,10 @@
         <v>0.8</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.969566</v>
+        <v>0.981228</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.013945</v>
+        <v>0.002283</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0.000104</v>
@@ -7814,10 +7814,10 @@
         <v>0.933376</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.875444</v>
+        <v>0.885975</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.904969</v>
+        <v>0.915855</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>0</v>
@@ -7834,10 +7834,10 @@
         <v>0.9</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.974371</v>
+        <v>0.981733</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.008847000000000001</v>
+        <v>0.001486</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.000115</v>
@@ -7861,10 +7861,10 @@
         <v>0.933376</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.876578</v>
+        <v>0.883201</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.909455</v>
+        <v>0.916326</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0.667</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.965882</v>
+        <v>0.983533</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.020925</v>
+        <v>0.003274</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>5.9e-05</v>
@@ -7908,10 +7908,10 @@
         <v>0.944968</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.895384</v>
+        <v>0.911747</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.912728</v>
+        <v>0.929408</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>1e-06</v>
@@ -7928,10 +7928,10 @@
         <v>0.8</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.972601</v>
+        <v>0.98433</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.013938</v>
+        <v>0.002209</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>6.999999999999999e-05</v>
@@ -7955,10 +7955,10 @@
         <v>0.944968</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.898315</v>
+        <v>0.909149</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.919077</v>
+        <v>0.93016</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>1e-06</v>
@@ -7975,10 +7975,10 @@
         <v>0.9</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.977508</v>
+        <v>0.984912</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.008835000000000001</v>
+        <v>0.001432</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>7.8e-05</v>
@@ -8002,10 +8002,10 @@
         <v>0.944968</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.900431</v>
+        <v>0.907251</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.923714</v>
+        <v>0.93071</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>1e-06</v>
